--- a/data/trans_dic/P1426-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1426-Edad-trans_dic.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,99</t>
+          <t>0,13; 1,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,97</t>
+          <t>0,15; 1,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,72</t>
+          <t>0,16; 1,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,7</t>
+          <t>0,53; 2,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,43</t>
+          <t>0,21; 1,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,7</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,57</t>
+          <t>0,35; 1,56</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,69</t>
+          <t>0,26; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,25</t>
+          <t>0,76; 2,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,63</t>
+          <t>0,15; 1,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,38</t>
+          <t>0,14; 1,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,71</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,27</t>
+          <t>0,33; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,82</t>
+          <t>0,14; 0,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,64</t>
+          <t>0,46; 1,63</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,69</t>
+          <t>0,17; 1,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,28</t>
+          <t>0,48; 2,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,93</t>
+          <t>2,08; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,14</t>
+          <t>0,49; 2,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,72</t>
+          <t>0,17; 1,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,05</t>
+          <t>1,44; 3,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,58</t>
+          <t>0,43; 1,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,62</t>
+          <t>0,48; 1,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,02</t>
+          <t>1,99; 3,65</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,46</t>
+          <t>1,23; 4,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,58</t>
+          <t>1,18; 4,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,89</t>
+          <t>4,05; 7,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,85</t>
+          <t>0,49; 2,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,97</t>
+          <t>1,55; 4,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,28</t>
+          <t>2,77; 5,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,12</t>
+          <t>1,08; 2,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,13</t>
+          <t>1,67; 4,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,18</t>
+          <t>3,81; 5,91</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,09</t>
+          <t>3,3; 9,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,58</t>
+          <t>0,6; 3,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,56; 11,14</t>
+          <t>6,48; 11,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,82</t>
+          <t>0,82; 3,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,25</t>
+          <t>4,43; 9,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,54</t>
+          <t>5,36; 9,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,33</t>
+          <t>2,4; 5,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,05</t>
+          <t>2,88; 5,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,2</t>
+          <t>6,36; 9,21</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,29</t>
+          <t>2,09; 7,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 11,99</t>
+          <t>5,63; 11,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,81; 23,92</t>
+          <t>16,87; 23,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,19</t>
+          <t>6,83; 13,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,38</t>
+          <t>3,37; 8,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,91; 23,34</t>
+          <t>17,59; 22,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,92</t>
+          <t>5,67; 10,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,74</t>
+          <t>5,04; 9,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,41; 22,71</t>
+          <t>17,98; 22,44</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,04</t>
+          <t>1,11; 2,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,94</t>
+          <t>1,07; 1,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,18</t>
+          <t>4,05; 5,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,35</t>
+          <t>1,41; 2,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,59</t>
+          <t>1,56; 2,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,96</t>
+          <t>4,14; 5,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,06</t>
+          <t>1,41; 2,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,09</t>
+          <t>1,45; 2,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 4,94</t>
+          <t>4,23; 5,05</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>2316</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 12303</t>
+          <t>0; 14079</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5410</t>
+          <t>0; 5054</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 14592</t>
+          <t>0; 13793</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7706</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>932; 13687</t>
+          <t>923; 13673</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1923,37 +1923,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7152</t>
+          <t>0; 6292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>936; 12014</t>
+          <t>946; 11202</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>901; 9684</t>
+          <t>876; 8881</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2694; 13796</t>
+          <t>2671; 12320</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2943; 18557</t>
+          <t>2776; 18201</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>900; 8120</t>
+          <t>896; 8848</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3480; 14716</t>
+          <t>3438; 15290</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>11751</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1808; 11536</t>
+          <t>1752; 10773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5376</t>
+          <t>0; 4587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4177; 17383</t>
+          <t>4726; 18356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1041; 11599</t>
+          <t>1053; 11843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>929; 9156</t>
+          <t>923; 8482</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>165; 3834</t>
+          <t>0; 5991</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4450; 17645</t>
+          <t>4659; 16712</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1820; 10917</t>
+          <t>1822; 10139</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5075; 17619</t>
+          <t>5703; 20185</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>22194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>38106</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1028; 10413</t>
+          <t>1051; 11000</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3154; 14724</t>
+          <t>3118; 14754</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8092; 34875</t>
+          <t>14545; 35186</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2140; 13141</t>
+          <t>2985; 13330</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1085; 11189</t>
+          <t>1095; 10902</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9202; 21688</t>
+          <t>10635; 23337</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5224; 19382</t>
+          <t>5239; 17555</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6437; 20926</t>
+          <t>6208; 20412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20065; 48255</t>
+          <t>28593; 52398</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>33759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>23641</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>53507</t>
+          <t>57400</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5460; 19146</t>
+          <t>5286; 19327</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5627; 21890</t>
+          <t>5626; 22255</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24136; 44182</t>
+          <t>24657; 45571</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2094; 12773</t>
+          <t>2188; 12909</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7666; 24694</t>
+          <t>7703; 24042</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14597; 28695</t>
+          <t>16795; 32404</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10456; 27343</t>
+          <t>9498; 25749</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16405; 40258</t>
+          <t>16323; 39043</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43333; 68201</t>
+          <t>46326; 71722</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>59833</t>
+          <t>64986</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10079; 28165</t>
+          <t>10231; 29123</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2058; 11960</t>
+          <t>2009; 11215</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24118; 40936</t>
+          <t>26336; 44828</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2921; 13522</t>
+          <t>2916; 13874</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16854; 34946</t>
+          <t>16741; 36024</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9598; 45822</t>
+          <t>23531; 39564</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15026; 35404</t>
+          <t>15948; 36367</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21402; 43087</t>
+          <t>20539; 41473</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30870; 80020</t>
+          <t>53763; 77821</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57782</t>
+          <t>62267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>94089</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>145351</t>
+          <t>156356</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5220; 18221</t>
+          <t>5215; 19047</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14935; 30822</t>
+          <t>14471; 30406</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47531; 67626</t>
+          <t>52329; 74155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26854; 51292</t>
+          <t>26557; 51865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13902; 33537</t>
+          <t>13502; 34381</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76246; 99347</t>
+          <t>81626; 106676</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35683; 63380</t>
+          <t>36242; 64149</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31885; 57414</t>
+          <t>33113; 59218</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>130407; 160861</t>
+          <t>139164; 173710</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>174510</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>314536</t>
+          <t>338620</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>38818; 69833</t>
+          <t>38013; 68462</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>36588; 65709</t>
+          <t>36336; 64386</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>118802; 179133</t>
+          <t>143078; 185982</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>50402; 83422</t>
+          <t>50236; 83816</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>57185; 91946</t>
+          <t>55309; 91540</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>130509; 181385</t>
+          <t>154437; 193746</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98274; 144032</t>
+          <t>98281; 147293</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>99982; 145331</t>
+          <t>100489; 148343</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>272030; 351359</t>
+          <t>307362; 366562</t>
         </is>
       </c>
     </row>
